--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/DISCO EMBREAGEM 05_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/DISCO EMBREAGEM 05_02.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>DESCRIÇÃO</t>
+          <t>DISCRIÇÃO</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMIRON TITAN FAN150 2005 A 2014/ FAN125 2009 039892</t>
+          <t>DISCO EMBREAGEM  IRON TITAN FAN150 2005 A 2014/ FAN125 2009 039892</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -470,7 +470,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMIRON CG FAN TITAN160 041441</t>
+          <t>DISCO EMBREAGEM  IRON CG FAN TITAN160 041441</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMCB300R/ XRE300 1151088</t>
+          <t>DISCO EMBREAGEM  CB300R/ XRE300 1151088</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMIRON FAZER YS250/ XTZ LANDER250 09865</t>
+          <t>DISCO EMBREAGEM  IRON FAZER YS250/ XTZ LANDISCO EMBREAGEM   R250 09865</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMIRON YBR125 2000 A 2008/ FACTOR125 2009 A 2016 014855</t>
+          <t>DISCO EMBREAGEM  IRON YBR125 2000 A 2008/ FACTOR125 2009 A 2016 014855</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMBRAVIC FAZER250/ LANDER250 BMA33011</t>
+          <t>DISCO EMBREAGEM  BRAVIC FAZER250/ LANDISCO EMBREAGEM   R250 BMA33011</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMCONTROLFLEX POP110I 2016</t>
+          <t>DISCO EMBREAGEM  CONTROLFLEX POP110I 2016</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMIRON FAZER150 039890</t>
+          <t>DISCO EMBREAGEM  IRON FAZER150 039890</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMIRON POP100 110I 039886</t>
+          <t>DISCO EMBREAGEM  IRON POP100 110I 039886</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMWGK YES125 1018641</t>
+          <t>DISCO EMBREAGEM  WGK YES125 1018641</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMGP YBR125 1102622</t>
+          <t>DISCO EMBREAGEM  GP YBR125 1102622</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMIRON CBX250 TWISTER 14856</t>
+          <t>DISCO EMBREAGEM  IRON CBX250 TWISTER 14856</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMPECA+ TRAXX JL50Q2/ SHINERAY WAVE110/ HUNTER125/ DAFRA ZIG50</t>
+          <t>DISCO EMBREAGEM  PECA+ TRAXX JL50Q2/ SHINERAY WAVE110/ HUNTER125/ DAFRA ZIG50</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMIRON BIZ125 014839</t>
+          <t>DISCO EMBREAGEM  IRON BIZ125 014839</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMIRON TITAN150 KS/ES 351241</t>
+          <t>DISCO EMBREAGEM  IRON TITAN150 KS/ES 351241</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMRIIE CBX250 TWISTER/ TORNADO250 000222</t>
+          <t>DISCO EMBREAGEM  RIIE CBX250 TWISTER/ TORNADO250 000222</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -793,7 +793,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMPANDAO SHINERAY50/ SUNDOWN HUNTER90</t>
+          <t>DISCO EMBREAGEM  PANDAO SHINERAY50/ SUNDOWN HUNTER90</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -814,7 +814,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMRT SHINERAY50</t>
+          <t>DISCO EMBREAGEM  RT SHINERAY50</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -835,7 +835,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMHONDA CG FAN TITAN150 160/ BROS150 160</t>
+          <t>DISCO EMBREAGEM  HONDA CG FAN TITAN150 160/ BROS150 160</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -856,7 +856,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMHONDA CG TITAN FAN150</t>
+          <t>DISCO EMBREAGEM  HONDA CG TITAN FAN150</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEMRT FAZER250 794400</t>
+          <t>DISCO EMBREAGEM  RT FAZER250 794400</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DE BRAVIC POP110I BMA32601</t>
+          <t>DISCO EMBREAGEM    BRAVIC POP110I BMA32601</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/DISCO EMBREAGEM 05_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/DISCO EMBREAGEM 05_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,11 +492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,7 +512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,7 +532,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,7 +552,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -579,7 +564,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEM  CONTROLFLEX POP110I 2016</t>
+          <t>DISCO EMBREAGEM VINI POP110I 2016</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -587,7 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -608,7 +592,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -629,7 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -650,11 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -675,7 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -696,7 +672,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -717,7 +692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -738,7 +712,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -759,7 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -780,11 +752,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -801,11 +768,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -822,11 +784,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -843,28 +800,26 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13021KGBAB00</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DISCO EMBREAGEM  HONDA CG TITAN FAN150</t>
+          <t>DISCO EMBREAGEM  HONDA POP</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -885,11 +840,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -910,11 +860,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -922,12 +867,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+          <t>22201KRM305</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DISCO EMBRAGEM HONDA CG TITAN FAN150 160/ BROS150 160</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
